--- a/docs/package/05_Delivery/Upload_Templates/Journal_Vouchers_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Journal_Vouchers_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t xml:space="preserve">Voucher Ref</t>
   </si>
@@ -207,12 +207,6 @@
     <t xml:space="preserve">Accounts &gt; Journal Voucher &gt; Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/journal-vouchers/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -222,7 +216,7 @@
     <t xml:space="preserve">Row limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Up to 1,000 data rows per file (Configuration setting limits.bulk_upload_max_rows) and 10 MB.</t>
+    <t xml:space="preserve">Up to 1,000 data rows per file and 10 MB.</t>
   </si>
   <si>
     <t xml:space="preserve">Required columns</t>
@@ -270,10 +264,10 @@
     <t xml:space="preserve">The sample account codes are from the TISPH chart of accounts; replace them with the accounts of your entries.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -281,7 +275,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -842,7 +836,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -938,34 +932,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15">
       <c r="B15" s="4" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Journal_Vouchers_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Journal_Vouchers_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
   <si>
     <t xml:space="preserve">Voucher Ref</t>
   </si>
@@ -129,7 +129,10 @@
     <t xml:space="preserve">date, documentDate, postingDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Transaction code (Master &gt; Finance &gt; Transaction Code); the same on every row of a voucher</t>
+    <t xml:space="preserve">An active transaction code (Master &gt; Finance &gt; Transaction Code); the same on every row of a voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JV</t>
   </si>
   <si>
     <t xml:space="preserve">transactionCode</t>
@@ -685,10 +688,10 @@
         <v>38</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -696,16 +699,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -716,13 +719,13 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -730,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -747,13 +750,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -761,16 +764,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -778,13 +781,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -792,13 +795,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -806,13 +809,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -820,13 +823,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -845,113 +848,113 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
